--- a/ruoyi-modules/ruoyi-procurement/src/main/resources/templates/最终模板_原项目归属参考.xlsx
+++ b/ruoyi-modules/ruoyi-procurement/src/main/resources/templates/最终模板_原项目归属参考.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\30224\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\jvkit\workspace\oa\ruoyi-6x\ruoyi-modules\ruoyi-procurement\src\main\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F698F5AA-AC96-435D-82CA-4691BE1700DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81FB7C3-8FAD-414C-B038-2FAC3B5D6D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5880" yWindow="3680" windowWidth="19200" windowHeight="11180" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
